--- a/data/gebze/Veriler.xlsx
+++ b/data/gebze/Veriler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\gebze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F857F4-DCE1-495A-8ED0-92B753E1B667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A169DBA0-A568-44A5-A7E7-24038F7BC2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="208">
   <si>
     <t>Traction_Converter</t>
   </si>
@@ -585,6 +585,9 @@
     <t>Arıza Tipi</t>
   </si>
   <si>
+    <t>GDM1</t>
+  </si>
+  <si>
     <t>MC</t>
   </si>
   <si>
@@ -594,6 +597,12 @@
     <t>(I) İlk Defa Karşılaşılan Arıza</t>
   </si>
   <si>
+    <t>GDM2</t>
+  </si>
+  <si>
+    <t>GEBZE</t>
+  </si>
+  <si>
     <t>SA</t>
   </si>
   <si>
@@ -606,6 +615,9 @@
     <t>(II) Aynı Araçta Tekrarlayan Arıza</t>
   </si>
   <si>
+    <t>GDM3</t>
+  </si>
+  <si>
     <t>T</t>
   </si>
   <si>
@@ -618,37 +630,34 @@
     <t>(III) Farklı Araçlarda Tekrarlayan Arıza</t>
   </si>
   <si>
+    <t>GDM4</t>
+  </si>
+  <si>
     <t>SB</t>
   </si>
   <si>
     <t>D-Arıza Değildir</t>
   </si>
   <si>
+    <t>GDM5</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
+    <t>GDM6</t>
+  </si>
+  <si>
     <t>GDM7</t>
   </si>
   <si>
-    <t>GEBZE</t>
-  </si>
-  <si>
-    <t>GDM1</t>
-  </si>
-  <si>
-    <t>GDM2</t>
-  </si>
-  <si>
-    <t>GDM3</t>
-  </si>
-  <si>
-    <t>GDM4</t>
-  </si>
-  <si>
-    <t>GDM5</t>
-  </si>
-  <si>
-    <t>GDM6</t>
+    <t>GEB7x4</t>
+  </si>
+  <si>
+    <t>İşçilik</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> £11,00 </t>
   </si>
 </sst>
 </file>
@@ -658,7 +667,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-41F]d\ mmmm\ yy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -703,13 +712,6 @@
       <color rgb="FF000000"/>
       <name val="Arial Nova Cond"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="162"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2353,7 +2355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
@@ -2362,7 +2364,7 @@
     <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>177</v>
       </c>
@@ -2381,115 +2383,121 @@
       <c r="F1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
         <v>43</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="G2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" t="s">
         <v>200</v>
       </c>
-      <c r="B3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D4" t="s">
-        <v>191</v>
-      </c>
-      <c r="E4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="C6" t="s">
         <v>202</v>
       </c>
-      <c r="C5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2529,7 +2537,6 @@
       <c r="A28" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/data/gebze/Veriler.xlsx
+++ b/data/gebze/Veriler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatiherkin\Desktop\bozankaya_ssh_takip\data\gebze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A169DBA0-A568-44A5-A7E7-24038F7BC2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671AD7E0-0416-415D-97E3-475F0583149D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="209">
   <si>
     <t>Traction_Converter</t>
   </si>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t xml:space="preserve"> £11,00 </t>
+  </si>
+  <si>
+    <t>Sıcaklık Sensörü</t>
   </si>
 </sst>
 </file>
@@ -1541,7 +1544,9 @@
         <v>86</v>
       </c>
       <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="C4" s="13" t="s">
+        <v>208</v>
+      </c>
       <c r="D4" s="10" t="s">
         <v>87</v>
       </c>
